--- a/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Ubuntu/Ubuntu_Data.xlsx
+++ b/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Ubuntu/Ubuntu_Data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29415"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19,8 +19,11 @@
     <sheet name="IPv6 - TCP" sheetId="3" r:id="rId4"/>
     <sheet name="IPv6 - UDP" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,6 +41,51 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="39">
+  <si>
+    <t>IPv4</t>
+  </si>
+  <si>
+    <t>IPv6</t>
+  </si>
+  <si>
+    <t>IPv4 TCP</t>
+  </si>
+  <si>
+    <t>IPv4 UDP</t>
+  </si>
+  <si>
+    <t>IPv6 TCP</t>
+  </si>
+  <si>
+    <t>IPv6 UDP</t>
+  </si>
+  <si>
+    <t>Packet Size</t>
+  </si>
+  <si>
+    <t>TCP Average Delay</t>
+  </si>
+  <si>
+    <t>TCP Jitter</t>
+  </si>
+  <si>
+    <t>TCP Bitrate</t>
+  </si>
+  <si>
+    <t>TCP Packet Loss</t>
+  </si>
+  <si>
+    <t>UDP Average Delay</t>
+  </si>
+  <si>
+    <t>UDP Jitter</t>
+  </si>
+  <si>
+    <t>UDP Bitrate</t>
+  </si>
+  <si>
+    <t>UDP Packet Loss</t>
+  </si>
   <si>
     <t>128</t>
   </si>
@@ -67,9 +115,6 @@
   </si>
   <si>
     <t>Average packet rate (pkt/s)</t>
-  </si>
-  <si>
-    <t>Packet Size</t>
   </si>
   <si>
     <t>Average Delay</t>
@@ -113,54 +158,12 @@
   <si>
     <t>1536</t>
   </si>
-  <si>
-    <t>IPv4 TCP</t>
-  </si>
-  <si>
-    <t>IPv4 UDP</t>
-  </si>
-  <si>
-    <t>IPv6 TCP</t>
-  </si>
-  <si>
-    <t>IPv6 UDP</t>
-  </si>
-  <si>
-    <t>TCP Average Delay</t>
-  </si>
-  <si>
-    <t>TCP Jitter</t>
-  </si>
-  <si>
-    <t>TCP Bitrate</t>
-  </si>
-  <si>
-    <t>TCP Packet Loss</t>
-  </si>
-  <si>
-    <t>UDP Average Delay</t>
-  </si>
-  <si>
-    <t>UDP Jitter</t>
-  </si>
-  <si>
-    <t>UDP Bitrate</t>
-  </si>
-  <si>
-    <t>UDP Packet Loss</t>
-  </si>
-  <si>
-    <t>IPv4</t>
-  </si>
-  <si>
-    <t>IPv6</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,10 +213,10 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9495,14 +9498,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F711C98E-99AA-4A88-97A9-146B9132475C}">
   <dimension ref="B2:AG18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="17" max="18" width="9.140625" style="2"/>
+    <col min="17" max="18" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:33">
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9518,7 +9521,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="T2" s="3" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
@@ -9534,7 +9537,7 @@
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
     </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:33">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -9564,99 +9567,99 @@
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
     </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="S5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="Y5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-    </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:33">
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="S5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="Y5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+    </row>
+    <row r="6" spans="2:33">
       <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
       <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" t="s">
+        <v>7</v>
+      </c>
+      <c r="U6" t="s">
+        <v>8</v>
+      </c>
+      <c r="V6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S6" t="s">
-        <v>10</v>
-      </c>
-      <c r="T6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6" t="s">
-        <v>30</v>
-      </c>
-      <c r="V6" t="s">
-        <v>31</v>
-      </c>
-      <c r="W6" t="s">
-        <v>32</v>
-      </c>
       <c r="Y6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33">
       <c r="B7">
         <v>128</v>
       </c>
@@ -9718,7 +9721,7 @@
         <v>5.1000000000000004E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:33">
       <c r="B8">
         <v>256</v>
       </c>
@@ -9780,7 +9783,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:33">
       <c r="B9">
         <v>384</v>
       </c>
@@ -9842,7 +9845,7 @@
         <v>0.10600000000000001</v>
       </c>
     </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:33">
       <c r="B10">
         <v>512</v>
       </c>
@@ -9904,7 +9907,7 @@
         <v>5.6000000000000008E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:33">
       <c r="B11">
         <v>640</v>
       </c>
@@ -9966,7 +9969,7 @@
         <v>0.11200000000000002</v>
       </c>
     </row>
-    <row r="12" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:33">
       <c r="B12">
         <v>768</v>
       </c>
@@ -10028,7 +10031,7 @@
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:33">
       <c r="B13">
         <v>896</v>
       </c>
@@ -10090,7 +10093,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:33">
       <c r="B14">
         <v>1024</v>
       </c>
@@ -10152,7 +10155,7 @@
         <v>8.3999999999999991E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:33">
       <c r="B15">
         <v>1152</v>
       </c>
@@ -10214,7 +10217,7 @@
         <v>4.0999999999999995E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:33">
       <c r="B16">
         <v>1280</v>
       </c>
@@ -10276,7 +10279,7 @@
         <v>3.9999999999999994E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:29">
       <c r="B17">
         <v>1408</v>
       </c>
@@ -10338,7 +10341,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:29">
       <c r="B18">
         <v>1536</v>
       </c>
@@ -10417,82 +10420,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10561,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>5</v>
       </c>
@@ -10630,7 +10633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>9</v>
       </c>
@@ -10699,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>3</v>
       </c>
@@ -10768,7 +10771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>2</v>
       </c>
@@ -10837,7 +10840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>6</v>
       </c>
@@ -10906,7 +10909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>4</v>
       </c>
@@ -10975,7 +10978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>8</v>
       </c>
@@ -11044,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>10</v>
       </c>
@@ -11113,7 +11116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>7</v>
       </c>
@@ -11182,9 +11185,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -11215,7 +11218,7 @@
         <v>16857.2790494</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -11265,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -11286,65 +11289,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -11394,7 +11397,7 @@
         <v>11443.541821000001</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>2</v>
       </c>
@@ -11444,7 +11447,7 @@
         <v>11438.461660000001</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>5</v>
       </c>
@@ -11494,7 +11497,7 @@
         <v>11415.416246000001</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>4</v>
       </c>
@@ -11544,7 +11547,7 @@
         <v>11438.544877</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>3</v>
       </c>
@@ -11594,7 +11597,7 @@
         <v>11429.108287999999</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>6</v>
       </c>
@@ -11644,7 +11647,7 @@
         <v>11424.861419999999</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>8</v>
       </c>
@@ -11694,7 +11697,7 @@
         <v>11460.377718</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>7</v>
       </c>
@@ -11744,7 +11747,7 @@
         <v>11415.698031</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>10</v>
       </c>
@@ -11794,7 +11797,7 @@
         <v>11416.689646000001</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>9</v>
       </c>
@@ -11844,9 +11847,9 @@
         <v>11419.770968999999</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -11877,7 +11880,7 @@
         <v>16966.778152799998</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -11908,65 +11911,65 @@
         <v>11430.247067600001</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -12016,7 +12019,7 @@
         <v>10181.23726</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>4</v>
       </c>
@@ -12066,7 +12069,7 @@
         <v>10175.677593</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>5</v>
       </c>
@@ -12116,7 +12119,7 @@
         <v>10168.101884</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>3</v>
       </c>
@@ -12166,7 +12169,7 @@
         <v>10153.9732</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>2</v>
       </c>
@@ -12216,7 +12219,7 @@
         <v>10160.282721</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>6</v>
       </c>
@@ -12266,7 +12269,7 @@
         <v>10154.866124</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>8</v>
       </c>
@@ -12316,7 +12319,7 @@
         <v>10147.983061000001</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>7</v>
       </c>
@@ -12366,7 +12369,7 @@
         <v>10175.338266000001</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>9</v>
       </c>
@@ -12416,7 +12419,7 @@
         <v>10143.389641</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>10</v>
       </c>
@@ -12466,9 +12469,9 @@
         <v>10163.856524000001</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -12499,7 +12502,7 @@
         <v>17109.476009700003</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -12530,65 +12533,65 @@
         <v>10162.470627400002</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -12638,7 +12641,7 @@
         <v>9172.9656180000002</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>2</v>
       </c>
@@ -12688,7 +12691,7 @@
         <v>9171.1071489999995</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>3</v>
       </c>
@@ -12738,7 +12741,7 @@
         <v>9143.1907190000002</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>5</v>
       </c>
@@ -12788,7 +12791,7 @@
         <v>9161.0753010000008</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>4</v>
       </c>
@@ -12838,7 +12841,7 @@
         <v>9140.2682650000006</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>6</v>
       </c>
@@ -12888,7 +12891,7 @@
         <v>9156.7068190000009</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>8</v>
       </c>
@@ -12938,7 +12941,7 @@
         <v>9134.443851</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>7</v>
       </c>
@@ -12988,7 +12991,7 @@
         <v>9127.8235929999992</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>9</v>
       </c>
@@ -13038,7 +13041,7 @@
         <v>9138.0524399999995</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>10</v>
       </c>
@@ -13088,9 +13091,9 @@
         <v>9166.7199739999996</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -13121,7 +13124,7 @@
         <v>17109.822890799998</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -13152,65 +13155,65 @@
         <v>9151.2353728999988</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>1</v>
       </c>
@@ -13260,7 +13263,7 @@
         <v>8346.6775510000007</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>3</v>
       </c>
@@ -13310,7 +13313,7 @@
         <v>8348.7000549999993</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>6</v>
       </c>
@@ -13360,7 +13363,7 @@
         <v>8319.5023039999996</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>7</v>
       </c>
@@ -13410,7 +13413,7 @@
         <v>8316.9788200000003</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>2</v>
       </c>
@@ -13460,7 +13463,7 @@
         <v>8309.5021739999993</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>4</v>
       </c>
@@ -13510,7 +13513,7 @@
         <v>8312.3193969999993</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>5</v>
       </c>
@@ -13560,7 +13563,7 @@
         <v>8317.8180119999997</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>8</v>
       </c>
@@ -13610,7 +13613,7 @@
         <v>8327.7413099999994</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>9</v>
       </c>
@@ -13660,7 +13663,7 @@
         <v>8305.9346619999997</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>10</v>
       </c>
@@ -13710,9 +13713,9 @@
         <v>8310.8672179999994</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -13743,7 +13746,7 @@
         <v>17179.687669999999</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -13774,65 +13777,65 @@
         <v>8321.6041502999997</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -13882,7 +13885,7 @@
         <v>7657.7346070000003</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>2</v>
       </c>
@@ -13932,7 +13935,7 @@
         <v>7655.8299530000004</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>8</v>
       </c>
@@ -13982,7 +13985,7 @@
         <v>7663.187876</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>3</v>
       </c>
@@ -14032,7 +14035,7 @@
         <v>7617.765496</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>6</v>
       </c>
@@ -14082,7 +14085,7 @@
         <v>7621.823934</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>7</v>
       </c>
@@ -14132,7 +14135,7 @@
         <v>7615.6155419999996</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>4</v>
       </c>
@@ -14182,7 +14185,7 @@
         <v>7609.5891730000003</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>9</v>
       </c>
@@ -14232,7 +14235,7 @@
         <v>7606.7826999999997</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>5</v>
       </c>
@@ -14282,7 +14285,7 @@
         <v>7614.6960989999998</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>10</v>
       </c>
@@ -14332,9 +14335,9 @@
         <v>7606.495269</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -14365,7 +14368,7 @@
         <v>15229.579464599999</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -14404,82 +14407,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>1</v>
       </c>
@@ -14548,7 +14551,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>2</v>
       </c>
@@ -14617,7 +14620,7 @@
         <v>5.5000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>6</v>
       </c>
@@ -14686,7 +14689,7 @@
         <v>5.5000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>4</v>
       </c>
@@ -14755,7 +14758,7 @@
         <v>0.12000000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>8</v>
       </c>
@@ -14824,7 +14827,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>5</v>
       </c>
@@ -14893,7 +14896,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>10</v>
       </c>
@@ -14962,7 +14965,7 @@
         <v>5.1000000000000004E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>9</v>
       </c>
@@ -15031,7 +15034,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>3</v>
       </c>
@@ -15100,7 +15103,7 @@
         <v>8.0999999999999989E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>7</v>
       </c>
@@ -15169,9 +15172,9 @@
         <v>3.9999999999999994E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -15202,7 +15205,7 @@
         <v>17062.409505899999</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -15252,7 +15255,7 @@
         <v>0.55499999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -15273,65 +15276,65 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>2</v>
       </c>
@@ -15381,7 +15384,7 @@
         <v>11409.469564999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>1</v>
       </c>
@@ -15431,7 +15434,7 @@
         <v>11406.96723</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>3</v>
       </c>
@@ -15481,7 +15484,7 @@
         <v>11382.212466000001</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>7</v>
       </c>
@@ -15531,7 +15534,7 @@
         <v>11380.905150000001</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>5</v>
       </c>
@@ -15581,7 +15584,7 @@
         <v>11382.907069000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>4</v>
       </c>
@@ -15631,7 +15634,7 @@
         <v>11380.869048</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>8</v>
       </c>
@@ -15681,7 +15684,7 @@
         <v>11383.067546</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>6</v>
       </c>
@@ -15731,7 +15734,7 @@
         <v>11382.874121999999</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>9</v>
       </c>
@@ -15781,7 +15784,7 @@
         <v>11381.205604999999</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>10</v>
       </c>
@@ -15831,9 +15834,9 @@
         <v>11383.255082</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -15864,7 +15867,7 @@
         <v>17060.610631700001</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -15895,65 +15898,65 @@
         <v>11387.373288299999</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -16003,7 +16006,7 @@
         <v>10221.085958</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>6</v>
       </c>
@@ -16053,7 +16056,7 @@
         <v>10217.314469000001</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>3</v>
       </c>
@@ -16103,7 +16106,7 @@
         <v>10185.612988999999</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>4</v>
       </c>
@@ -16153,7 +16156,7 @@
         <v>10185.293658000001</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>7</v>
       </c>
@@ -16203,7 +16206,7 @@
         <v>10184.641677</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>9</v>
       </c>
@@ -16253,7 +16256,7 @@
         <v>10185.33308</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>10</v>
       </c>
@@ -16303,7 +16306,7 @@
         <v>10184.543749</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>2</v>
       </c>
@@ -16353,7 +16356,7 @@
         <v>10187.231879999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>5</v>
       </c>
@@ -16403,7 +16406,7 @@
         <v>10186.278108</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>8</v>
       </c>
@@ -16453,9 +16456,9 @@
         <v>10187.362584</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -16486,7 +16489,7 @@
         <v>17036.444199500002</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -16517,65 +16520,65 @@
         <v>10192.469815200002</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>2</v>
       </c>
@@ -16625,7 +16628,7 @@
         <v>9284.4154240000007</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>1</v>
       </c>
@@ -16675,7 +16678,7 @@
         <v>9282.5953539999991</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>4</v>
       </c>
@@ -16725,7 +16728,7 @@
         <v>9232.4635259999995</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>3</v>
       </c>
@@ -16775,7 +16778,7 @@
         <v>9230.5813089999992</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>9</v>
       </c>
@@ -16825,7 +16828,7 @@
         <v>9231.2831000000006</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>5</v>
       </c>
@@ -16875,7 +16878,7 @@
         <v>9232.3641389999993</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>8</v>
       </c>
@@ -16925,7 +16928,7 @@
         <v>9230.9002419999997</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>6</v>
       </c>
@@ -16975,7 +16978,7 @@
         <v>9232.5070039999991</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>10</v>
       </c>
@@ -17025,7 +17028,7 @@
         <v>9231.7352040000005</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>7</v>
       </c>
@@ -17075,9 +17078,9 @@
         <v>9231.0574250000009</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -17108,7 +17111,7 @@
         <v>17053.487327700001</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -17139,65 +17142,65 @@
         <v>9241.990272699999</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>1</v>
       </c>
@@ -17247,7 +17250,7 @@
         <v>9419.8722240000006</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>2</v>
       </c>
@@ -17297,7 +17300,7 @@
         <v>4784.1048019999998</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>10</v>
       </c>
@@ -17347,7 +17350,7 @@
         <v>9359.3449390000005</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>3</v>
       </c>
@@ -17397,7 +17400,7 @@
         <v>9357.9338480000006</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>4</v>
       </c>
@@ -17447,7 +17450,7 @@
         <v>9358.4839589999992</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>9</v>
       </c>
@@ -17497,7 +17500,7 @@
         <v>9357.8670810000003</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>5</v>
       </c>
@@ -17547,7 +17550,7 @@
         <v>9357.9663500000006</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>8</v>
       </c>
@@ -17597,7 +17600,7 @@
         <v>4726.0822230000003</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>7</v>
       </c>
@@ -17647,7 +17650,7 @@
         <v>9359.1687309999998</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>6</v>
       </c>
@@ -17697,9 +17700,9 @@
         <v>9359.113464</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -17730,7 +17733,7 @@
         <v>17061.1044549</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -17761,65 +17764,65 @@
         <v>8443.9937621000008</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -17869,7 +17872,7 @@
         <v>7530.3335770000003</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>3</v>
       </c>
@@ -17919,7 +17922,7 @@
         <v>7529.7173599999996</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>8</v>
       </c>
@@ -17969,7 +17972,7 @@
         <v>7459.2620260000003</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>10</v>
       </c>
@@ -18019,7 +18022,7 @@
         <v>7458.4750119999999</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>4</v>
       </c>
@@ -18069,7 +18072,7 @@
         <v>7457.6739449999995</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>7</v>
       </c>
@@ -18119,7 +18122,7 @@
         <v>7458.1730900000002</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>2</v>
       </c>
@@ -18169,7 +18172,7 @@
         <v>7457.0325439999997</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>5</v>
       </c>
@@ -18219,7 +18222,7 @@
         <v>7458.3353699999998</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>6</v>
       </c>
@@ -18269,7 +18272,7 @@
         <v>7458.0228159999997</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>9</v>
       </c>
@@ -18319,9 +18322,9 @@
         <v>7458.4400930000002</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -18352,7 +18355,7 @@
         <v>14815.212995899998</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -18391,82 +18394,82 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>1</v>
       </c>
@@ -18535,7 +18538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>2</v>
       </c>
@@ -18604,7 +18607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>4</v>
       </c>
@@ -18673,7 +18676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>3</v>
       </c>
@@ -18742,7 +18745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>5</v>
       </c>
@@ -18811,7 +18814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>7</v>
       </c>
@@ -18880,7 +18883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>8</v>
       </c>
@@ -18949,7 +18952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>6</v>
       </c>
@@ -19018,7 +19021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>9</v>
       </c>
@@ -19087,7 +19090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>10</v>
       </c>
@@ -19156,9 +19159,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -19189,7 +19192,7 @@
         <v>16859.5045943</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -19239,7 +19242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -19260,65 +19263,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>4</v>
       </c>
@@ -19368,7 +19371,7 @@
         <v>11436.581582999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>1</v>
       </c>
@@ -19418,7 +19421,7 @@
         <v>11436.201356</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>2</v>
       </c>
@@ -19468,7 +19471,7 @@
         <v>11418.085107999999</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>5</v>
       </c>
@@ -19518,7 +19521,7 @@
         <v>11432.171988</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>8</v>
       </c>
@@ -19568,7 +19571,7 @@
         <v>11439.518754000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>3</v>
       </c>
@@ -19618,7 +19621,7 @@
         <v>11421.077246999999</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>6</v>
       </c>
@@ -19668,7 +19671,7 @@
         <v>11422.423769000001</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>7</v>
       </c>
@@ -19718,7 +19721,7 @@
         <v>11421.312733000001</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>9</v>
       </c>
@@ -19768,7 +19771,7 @@
         <v>11427.037832</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>10</v>
       </c>
@@ -19818,9 +19821,9 @@
         <v>11451.757615</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -19851,7 +19854,7 @@
         <v>17012.920951200002</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -19882,65 +19885,65 @@
         <v>11430.616798499999</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -19990,7 +19993,7 @@
         <v>10179.141111999999</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>4</v>
       </c>
@@ -20040,7 +20043,7 @@
         <v>10174.906443</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>2</v>
       </c>
@@ -20090,7 +20093,7 @@
         <v>10160.143953999999</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>3</v>
       </c>
@@ -20140,7 +20143,7 @@
         <v>10156.40093</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>7</v>
       </c>
@@ -20190,7 +20193,7 @@
         <v>10163.487325</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>5</v>
       </c>
@@ -20240,7 +20243,7 @@
         <v>10168.087960000001</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>8</v>
       </c>
@@ -20290,7 +20293,7 @@
         <v>10152.783740999999</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>6</v>
       </c>
@@ -20340,7 +20343,7 @@
         <v>10160.466253000001</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>9</v>
       </c>
@@ -20390,7 +20393,7 @@
         <v>10152.888308</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>10</v>
       </c>
@@ -20440,9 +20443,9 @@
         <v>10165.024205</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -20473,7 +20476,7 @@
         <v>17108.307474399997</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -20504,65 +20507,65 @@
         <v>10163.333023099998</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -20612,7 +20615,7 @@
         <v>9168.2584330000009</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>4</v>
       </c>
@@ -20662,7 +20665,7 @@
         <v>9166.1190200000001</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>2</v>
       </c>
@@ -20712,7 +20715,7 @@
         <v>9142.4531040000002</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>3</v>
       </c>
@@ -20762,7 +20765,7 @@
         <v>9151.9358890000003</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>5</v>
       </c>
@@ -20812,7 +20815,7 @@
         <v>9137.7086259999996</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>7</v>
       </c>
@@ -20862,7 +20865,7 @@
         <v>9148.9216589999996</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>6</v>
       </c>
@@ -20912,7 +20915,7 @@
         <v>9132.7086039999995</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>8</v>
       </c>
@@ -20962,7 +20965,7 @@
         <v>9136.5740769999993</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>9</v>
       </c>
@@ -21012,7 +21015,7 @@
         <v>9130.4294200000004</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>10</v>
       </c>
@@ -21062,9 +21065,9 @@
         <v>9127.1063489999997</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -21095,7 +21098,7 @@
         <v>17106.111212600001</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -21126,65 +21129,65 @@
         <v>9144.2215180999992</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>1</v>
       </c>
@@ -21234,7 +21237,7 @@
         <v>8346.9420470000005</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>5</v>
       </c>
@@ -21284,7 +21287,7 @@
         <v>8344.2691369999993</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>3</v>
       </c>
@@ -21334,7 +21337,7 @@
         <v>8314.0774359999996</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>2</v>
       </c>
@@ -21384,7 +21387,7 @@
         <v>8323.8874180000003</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>6</v>
       </c>
@@ -21434,7 +21437,7 @@
         <v>8323.3438650000007</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>4</v>
       </c>
@@ -21484,7 +21487,7 @@
         <v>8303.7968540000002</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>9</v>
       </c>
@@ -21534,7 +21537,7 @@
         <v>8309.3612830000002</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>7</v>
       </c>
@@ -21584,7 +21587,7 @@
         <v>8297.3724739999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>8</v>
       </c>
@@ -21634,7 +21637,7 @@
         <v>8316.6862660000006</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>10</v>
       </c>
@@ -21684,9 +21687,9 @@
         <v>8301.407588</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -21717,7 +21720,7 @@
         <v>17179.049982799999</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -21748,65 +21751,65 @@
         <v>8318.1144368000005</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -21856,7 +21859,7 @@
         <v>7663.3069800000003</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>3</v>
       </c>
@@ -21906,7 +21909,7 @@
         <v>7661.380349</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>2</v>
       </c>
@@ -21956,7 +21959,7 @@
         <v>7638.944853</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>4</v>
       </c>
@@ -22006,7 +22009,7 @@
         <v>7626.3508860000002</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>5</v>
       </c>
@@ -22056,7 +22059,7 @@
         <v>7634.2569460000004</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>6</v>
       </c>
@@ -22106,7 +22109,7 @@
         <v>7649.3181990000003</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>8</v>
       </c>
@@ -22156,7 +22159,7 @@
         <v>7616.0750019999996</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>9</v>
       </c>
@@ -22206,7 +22209,7 @@
         <v>7628.2825919999996</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>10</v>
       </c>
@@ -22256,7 +22259,7 @@
         <v>7641.6622880000004</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>7</v>
       </c>
@@ -22306,9 +22309,9 @@
         <v>7617.2243120000003</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -22339,7 +22342,7 @@
         <v>15229.758164399998</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -22378,82 +22381,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>1</v>
       </c>
@@ -22522,7 +22525,7 @@
         <v>5.1000000000000004E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>5</v>
       </c>
@@ -22591,7 +22594,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>4</v>
       </c>
@@ -22660,7 +22663,7 @@
         <v>0.10600000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>7</v>
       </c>
@@ -22729,7 +22732,7 @@
         <v>5.6000000000000008E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>6</v>
       </c>
@@ -22798,7 +22801,7 @@
         <v>0.11200000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>10</v>
       </c>
@@ -22867,7 +22870,7 @@
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>9</v>
       </c>
@@ -22936,7 +22939,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>3</v>
       </c>
@@ -23005,7 +23008,7 @@
         <v>8.3999999999999991E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>8</v>
       </c>
@@ -23074,7 +23077,7 @@
         <v>4.0999999999999995E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>2</v>
       </c>
@@ -23143,9 +23146,9 @@
         <v>3.9999999999999994E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -23176,7 +23179,7 @@
         <v>17024.316021099999</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -23226,7 +23229,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -23247,65 +23250,65 @@
         <v>4.1999999999999996E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>5</v>
       </c>
@@ -23355,7 +23358,7 @@
         <v>11405.11838</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>4</v>
       </c>
@@ -23405,7 +23408,7 @@
         <v>11405.568601000001</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>2</v>
       </c>
@@ -23455,7 +23458,7 @@
         <v>11378.901777999999</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>3</v>
       </c>
@@ -23505,7 +23508,7 @@
         <v>11377.93252</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>1</v>
       </c>
@@ -23555,7 +23558,7 @@
         <v>11377.607475000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>10</v>
       </c>
@@ -23605,7 +23608,7 @@
         <v>11377.714882</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>6</v>
       </c>
@@ -23655,7 +23658,7 @@
         <v>11378.716576999999</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>7</v>
       </c>
@@ -23705,7 +23708,7 @@
         <v>11377.497884</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>9</v>
       </c>
@@ -23755,7 +23758,7 @@
         <v>11380.152104999999</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>8</v>
       </c>
@@ -23805,9 +23808,9 @@
         <v>11380.002506999999</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -23838,7 +23841,7 @@
         <v>17051.157971700002</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -23869,65 +23872,65 @@
         <v>11383.9212709</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -23977,7 +23980,7 @@
         <v>10219.637559000001</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>5</v>
       </c>
@@ -24027,7 +24030,7 @@
         <v>10217.944852000001</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>4</v>
       </c>
@@ -24077,7 +24080,7 @@
         <v>10189.736825</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>8</v>
       </c>
@@ -24127,7 +24130,7 @@
         <v>10188.574387000001</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>3</v>
       </c>
@@ -24177,7 +24180,7 @@
         <v>10188.806764999999</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>2</v>
       </c>
@@ -24227,7 +24230,7 @@
         <v>10187.783656</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>10</v>
       </c>
@@ -24277,7 +24280,7 @@
         <v>10188.698482</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>7</v>
       </c>
@@ -24327,7 +24330,7 @@
         <v>10188.161807</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>9</v>
       </c>
@@ -24377,7 +24380,7 @@
         <v>10189.162469000001</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>6</v>
       </c>
@@ -24427,9 +24430,9 @@
         <v>10189.476747999999</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -24460,7 +24463,7 @@
         <v>17035.870682100001</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -24491,65 +24494,65 @@
         <v>10194.798355000001</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -24599,7 +24602,7 @@
         <v>9269.8251130000008</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>4</v>
       </c>
@@ -24649,7 +24652,7 @@
         <v>9268.5534669999997</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>2</v>
       </c>
@@ -24699,7 +24702,7 @@
         <v>9226.1869370000004</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>5</v>
       </c>
@@ -24749,7 +24752,7 @@
         <v>9227.0275880000008</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>9</v>
       </c>
@@ -24799,7 +24802,7 @@
         <v>9225.1141960000004</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>10</v>
       </c>
@@ -24849,7 +24852,7 @@
         <v>9226.3941849999992</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>6</v>
       </c>
@@ -24899,7 +24902,7 @@
         <v>9227.1861800000006</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>3</v>
       </c>
@@ -24949,7 +24952,7 @@
         <v>9227.3729270000003</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>7</v>
       </c>
@@ -24999,7 +25002,7 @@
         <v>9224.9498760000006</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>8</v>
       </c>
@@ -25049,9 +25052,9 @@
         <v>9224.9058060000007</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -25082,7 +25085,7 @@
         <v>17047.003811900002</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -25113,65 +25116,65 @@
         <v>9234.7516274999998</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>1</v>
       </c>
@@ -25221,7 +25224,7 @@
         <v>8479.4957400000003</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>2</v>
       </c>
@@ -25271,7 +25274,7 @@
         <v>8478.8145519999998</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>4</v>
       </c>
@@ -25321,7 +25324,7 @@
         <v>8427.6187460000001</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>8</v>
       </c>
@@ -25371,7 +25374,7 @@
         <v>8427.7246890000006</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>6</v>
       </c>
@@ -25421,7 +25424,7 @@
         <v>8425.9946209999998</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>3</v>
       </c>
@@ -25471,7 +25474,7 @@
         <v>8426.7066109999996</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>7</v>
       </c>
@@ -25521,7 +25524,7 @@
         <v>8426.0583549999992</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>5</v>
       </c>
@@ -25571,7 +25574,7 @@
         <v>8426.3525269999991</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>10</v>
       </c>
@@ -25621,7 +25624,7 @@
         <v>8427.1849899999997</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>9</v>
       </c>
@@ -25671,9 +25674,9 @@
         <v>8428.1603830000004</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -25704,7 +25707,7 @@
         <v>17040.997126399998</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -25735,65 +25738,65 @@
         <v>8437.4111213999986</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -25843,7 +25846,7 @@
         <v>7515.5318289999996</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>2</v>
       </c>
@@ -25893,7 +25896,7 @@
         <v>7516.39138</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>6</v>
       </c>
@@ -25943,7 +25946,7 @@
         <v>7455.8937660000001</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>8</v>
       </c>
@@ -25993,7 +25996,7 @@
         <v>7455.3657450000001</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>7</v>
       </c>
@@ -26043,7 +26046,7 @@
         <v>7453.4231019999997</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>5</v>
       </c>
@@ -26093,7 +26096,7 @@
         <v>7454.3389880000004</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>3</v>
       </c>
@@ -26143,7 +26146,7 @@
         <v>7454.0189730000002</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>9</v>
       </c>
@@ -26193,7 +26196,7 @@
         <v>7454.1737810000004</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>4</v>
       </c>
@@ -26243,7 +26246,7 @@
         <v>7453.1702660000001</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>10</v>
       </c>
@@ -26293,9 +26296,9 @@
         <v>7453.9740819999997</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -26326,7 +26329,7 @@
         <v>14830.673424999997</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
